--- a/03_Outputs/Agua_Bosques_Turismo/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Agua_Bosques_Turismo/03_Ordenamiento/ordenamiento.xlsx
@@ -148,7 +148,7 @@
     <numFmt numFmtId="272" formatCode="#,##0.0"/>
     <numFmt numFmtId="273" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,23 +158,335 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -194,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -203,111 +515,167 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="169" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="170" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="171" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="172" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="172" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="173" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="174" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="175" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="176" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="176" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="177" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="178" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="178" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="179" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="182" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="10" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="12" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="240" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="246" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="252" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="253" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="254" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="254" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="255" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="256" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="256" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="257" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="258" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="258" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="259" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="260" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="260" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="261" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="14" numFmtId="262" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="15" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="263" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="16" numFmtId="264" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="17" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="265" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="266" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="266" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="267" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="268" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="268" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="269" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="270" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="270" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="271" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="18" numFmtId="272" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="19" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="273" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="12" fontId="20" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="13" fontId="21" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="14" fontId="22" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="15" fontId="23" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="16" fontId="24" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="17" fontId="25" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="18" fontId="26" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="19" fontId="27" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="20" fontId="28" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="21" fontId="29" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="22" fontId="30" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="23" fontId="31" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="24" fontId="32" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="25" fontId="33" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="34" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="26" fontId="34" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,12 +1004,12 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="88.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="89.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1084,35 +1452,35 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="137" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="137" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="137" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="137" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="137" t="inlineStr">
         <is>
           <t>Predios con uso adecuado del suelo rural</t>
         </is>
@@ -1137,7 +1505,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="112">
+      <c r="E2" s="138">
         <v>0.382372461061085</v>
       </c>
     </row>
@@ -1160,7 +1528,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="112">
+      <c r="E3" s="138">
         <v>0.413116055348241</v>
       </c>
     </row>
@@ -1183,7 +1551,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="112">
+      <c r="E4" s="138">
         <v>0.246621726402192</v>
       </c>
     </row>
@@ -1206,7 +1574,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="112" t="inlineStr">
+      <c r="E5" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1231,7 +1599,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="112">
+      <c r="E6" s="138">
         <v>0.272540531317434</v>
       </c>
     </row>
@@ -1254,7 +1622,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="112" t="inlineStr">
+      <c r="E7" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1279,7 +1647,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="112" t="inlineStr">
+      <c r="E8" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1304,7 +1672,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="112">
+      <c r="E9" s="138">
         <v>0.503491646142619</v>
       </c>
     </row>
@@ -1327,7 +1695,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="112">
+      <c r="E10" s="138">
         <v>0.680957830500501</v>
       </c>
     </row>
@@ -1350,7 +1718,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="112" t="inlineStr">
+      <c r="E11" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1375,7 +1743,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="112">
+      <c r="E12" s="138">
         <v>0.466490176108494</v>
       </c>
     </row>
@@ -1398,7 +1766,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="112" t="inlineStr">
+      <c r="E13" s="138" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -1416,17 +1784,17 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="140" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="140" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1514,17 +1882,17 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="142" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="142" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -1642,23 +2010,22 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="144" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="144" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2216,23 +2583,23 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="146" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="146" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="146" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2790,17 +3157,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="148" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="148" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -2938,16 +3305,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="150" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="150" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3085,23 +3453,23 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="152" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="152" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3299,22 +3667,23 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="154" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="154" t="inlineStr">
         <is>
           <t>serie</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="154" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3662,17 +4031,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="156" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="156" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -3810,101 +4179,101 @@
   <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (municipal)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de energía (agregado)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (municipal)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de acueducto (agregado)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (municipal)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de alcantarillado (agregado)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (municipal)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de recolección de basuras (agregado)</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (municipal)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de internet (agregado)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (municipal)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Cobertura de gas natural (agregado)</t>
         </is>
@@ -3929,50 +4298,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>0.982396190132805</v>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" s="15">
         <v>0.885636380025239</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I2" s="16">
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" s="19">
         <v>0.618154858482063</v>
       </c>
-      <c r="J2" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K2" s="20">
+      <c r="J2" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" s="23">
         <v>0.638672255273122</v>
       </c>
-      <c r="L2" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M2" s="24">
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" s="27">
         <v>0.387283817078301</v>
       </c>
-      <c r="N2" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O2" s="28">
+      <c r="N2" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" s="31">
         <v>0</v>
       </c>
-      <c r="P2" s="30" t="inlineStr">
+      <c r="P2" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -3997,50 +4366,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>0.99358787593985</v>
       </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G3" s="12">
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" s="15">
         <v>0.969120089765229</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I3" s="16">
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" s="19">
         <v>0.674162382998312</v>
       </c>
-      <c r="J3" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K3" s="20">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" s="23">
         <v>0.961018681908854</v>
       </c>
-      <c r="L3" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M3" s="24">
+      <c r="L3" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" s="27">
         <v>0.350995425425809</v>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O3" s="28">
+      <c r="N3" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" s="31">
         <v>0.329579081632653</v>
       </c>
-      <c r="P3" s="30" t="inlineStr">
+      <c r="P3" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4065,50 +4434,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>0.993448858833474</v>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G4" s="12">
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" s="15">
         <v>0.692096365173288</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I4" s="16">
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" s="19">
         <v>0.528317836010143</v>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K4" s="20">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" s="23">
         <v>0.737954353338968</v>
       </c>
-      <c r="L4" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M4" s="24">
+      <c r="L4" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M4" s="27">
         <v>0.250565610859728</v>
       </c>
-      <c r="N4" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O4" s="28">
+      <c r="N4" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" s="31">
         <v>0.467586146884789</v>
       </c>
-      <c r="P4" s="30" t="inlineStr">
+      <c r="P4" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4133,50 +4502,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>0.987541541836517</v>
       </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" s="12">
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="15">
         <v>0.96011179009833</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I5" s="16">
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="19">
         <v>0.779464146727833</v>
       </c>
-      <c r="J5" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K5" s="20">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="23">
         <v>0.730869111964076</v>
       </c>
-      <c r="L5" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M5" s="24">
+      <c r="L5" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" s="27">
         <v>0.204537199592552</v>
       </c>
-      <c r="N5" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O5" s="28">
+      <c r="N5" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" s="31">
         <v>0.374282339367634</v>
       </c>
-      <c r="P5" s="30" t="inlineStr">
+      <c r="P5" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4201,50 +4570,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>0.996482898377522</v>
       </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" s="12">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="15">
         <v>0.982414491887609</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" s="16">
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="19">
         <v>0.883935646458217</v>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" s="20">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="23">
         <v>0.955337880575926</v>
       </c>
-      <c r="L6" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M6" s="24">
+      <c r="L6" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M6" s="27">
         <v>0.58860053379805</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O6" s="28">
+      <c r="N6" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" s="31">
         <v>0.803766014191314</v>
       </c>
-      <c r="P6" s="30" t="inlineStr">
+      <c r="P6" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4269,50 +4638,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>1</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G7" s="12">
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" s="15">
         <v>0.990118147534265</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I7" s="16">
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I7" s="19">
         <v>0.822126655616778</v>
       </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K7" s="20">
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" s="23">
         <v>0.980718275951891</v>
       </c>
-      <c r="L7" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M7" s="24">
+      <c r="L7" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" s="27">
         <v>0.721619953510828</v>
       </c>
-      <c r="N7" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O7" s="28">
+      <c r="N7" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" s="31">
         <v>0.741865639325658</v>
       </c>
-      <c r="P7" s="30" t="inlineStr">
+      <c r="P7" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4337,50 +4706,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>1</v>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G8" s="12">
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" s="15">
         <v>0.992776569882714</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I8" s="16">
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I8" s="19">
         <v>0.609934773666582</v>
       </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K8" s="20">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" s="23">
         <v>0.948709899251493</v>
       </c>
-      <c r="L8" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M8" s="24">
+      <c r="L8" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="27">
         <v>0.481941424706786</v>
       </c>
-      <c r="N8" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O8" s="28">
+      <c r="N8" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="31">
         <v>0.564415923180344</v>
       </c>
-      <c r="P8" s="30" t="inlineStr">
+      <c r="P8" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4405,50 +4774,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>0.989304252615643</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G9" s="12">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" s="15">
         <v>0.937325015545162</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I9" s="16">
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I9" s="19">
         <v>0.561907774383375</v>
       </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K9" s="20">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" s="23">
         <v>0.875716113799598</v>
       </c>
-      <c r="L9" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M9" s="24">
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="27">
         <v>0.207483531139888</v>
       </c>
-      <c r="N9" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O9" s="28">
+      <c r="N9" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="31">
         <v>0.359555408364649</v>
       </c>
-      <c r="P9" s="30" t="inlineStr">
+      <c r="P9" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4473,50 +4842,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>0.985834722460264</v>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G10" s="12">
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" s="15">
         <v>0.82859535123758</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I10" s="16">
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I10" s="19">
         <v>0.590677701812119</v>
       </c>
-      <c r="J10" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K10" s="20">
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" s="23">
         <v>0.979021670380124</v>
       </c>
-      <c r="L10" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M10" s="24">
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="27">
         <v>0.259631354277563</v>
       </c>
-      <c r="N10" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O10" s="28">
+      <c r="N10" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" s="31">
         <v>0</v>
       </c>
-      <c r="P10" s="30" t="inlineStr">
+      <c r="P10" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4541,50 +4910,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>1</v>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G11" s="12">
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" s="15">
         <v>0.928224227633555</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I11" s="16">
+      <c r="H11" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I11" s="19">
         <v>0.765744374048278</v>
       </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K11" s="20">
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K11" s="23">
         <v>0.978707022072098</v>
       </c>
-      <c r="L11" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M11" s="24">
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="27">
         <v>0.461351507187299</v>
       </c>
-      <c r="N11" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O11" s="28">
+      <c r="N11" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" s="31">
         <v>0.586711836934396</v>
       </c>
-      <c r="P11" s="30" t="inlineStr">
+      <c r="P11" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4609,50 +4978,50 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>0.981027805251874</v>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G12" s="12">
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" s="15">
         <v>0.870586502982463</v>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I12" s="16">
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I12" s="19">
         <v>0.614163050122375</v>
       </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" s="20">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" s="23">
         <v>0.731644219482237</v>
       </c>
-      <c r="L12" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M12" s="24">
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="27">
         <v>0.280251894612758</v>
       </c>
-      <c r="N12" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O12" s="28">
+      <c r="N12" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" s="31">
         <v>0.486420903887225</v>
       </c>
-      <c r="P12" s="30" t="inlineStr">
+      <c r="P12" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -4677,262 +5046,262 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>0.994623018561171</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" s="15">
         <v>0.975741657185578</v>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I13" s="16">
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I13" s="19">
         <v>0.473762666844046</v>
       </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K13" s="20">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" s="23">
         <v>0.924443591327782</v>
       </c>
-      <c r="L13" s="22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M13" s="24">
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="27">
         <v>0.44743509670711</v>
       </c>
-      <c r="N13" s="26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O13" s="28">
+      <c r="N13" s="29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" s="31">
         <v>0.3903575282025</v>
       </c>
-      <c r="P13" s="30" t="inlineStr">
+      <c r="P13" s="33" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>PROVINCIA AGUA, BOSQUES Y TURISMO (ECV oficial)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F14" s="11">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" s="14">
         <v>0.994710280724391</v>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H14" s="15">
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H14" s="18">
         <v>0.952761375632215</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J14" s="19">
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" s="22">
         <v>0.689831788695208</v>
       </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L14" s="23">
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" s="26">
         <v>0.912312503103018</v>
       </c>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N14" s="27">
+      <c r="M14" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" s="30">
         <v>0.476647084980336</v>
       </c>
-      <c r="O14" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P14" s="31">
+      <c r="O14" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" s="34">
         <v>0.528188153360459</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SUBREGIÓN ORIENTE (ECV oficial)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F15" s="11">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" s="14">
         <v>0.995718416345984</v>
       </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H15" s="15">
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H15" s="18">
         <v>0.946340911142438</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J15" s="19">
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" s="22">
         <v>0.732373921372333</v>
       </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L15" s="23">
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" s="26">
         <v>0.890202455202672</v>
       </c>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N15" s="27">
+      <c r="M15" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" s="30">
         <v>0.536468604306933</v>
       </c>
-      <c r="O15" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P15" s="31">
+      <c r="O15" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" s="34">
         <v>0.50840292380379</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>DEPARTAMENTO (ANTIOQUIA) (ECV oficial)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F16" s="11">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" s="14">
         <v>0.992586544500931</v>
       </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H16" s="15">
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H16" s="18">
         <v>0.93579635079431</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J16" s="19">
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" s="22">
         <v>0.866893560801633</v>
       </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L16" s="23">
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" s="26">
         <v>0.944698426552535</v>
       </c>
-      <c r="M16" s="25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N16" s="27">
+      <c r="M16" s="28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" s="30">
         <v>0.601239746666835</v>
       </c>
-      <c r="O16" s="29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P16" s="31">
+      <c r="O16" s="32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" s="34">
         <v>0.66955125810138</v>
       </c>
     </row>
@@ -4948,17 +5317,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="158" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="158" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5096,17 +5465,17 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="160" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="160" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5234,17 +5603,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="162" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="162" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5382,17 +5751,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="164" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="164" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5405,7 +5774,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>277.010406811731</v>
+        <v>70.5771050141911</v>
       </c>
     </row>
     <row r="3">
@@ -5415,7 +5784,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>788.053949903661</v>
+        <v>149.667474672136</v>
       </c>
     </row>
     <row r="4">
@@ -5425,7 +5794,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>91.1580594679186</v>
+        <v>25.6259780907668</v>
       </c>
     </row>
     <row r="5">
@@ -5435,7 +5804,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>678.432118732756</v>
+        <v>165.065169822091</v>
       </c>
     </row>
     <row r="6">
@@ -5445,7 +5814,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>942.6508509541</v>
+        <v>261.165549252192</v>
       </c>
     </row>
     <row r="7">
@@ -5455,7 +5824,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>870.896625890577</v>
+        <v>297.002285253394</v>
       </c>
     </row>
     <row r="8">
@@ -5465,7 +5834,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>1045.70445293155</v>
+        <v>236.748226801528</v>
       </c>
     </row>
     <row r="9">
@@ -5475,7 +5844,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>713.012162002598</v>
+        <v>192.938953831621</v>
       </c>
     </row>
     <row r="10">
@@ -5485,7 +5854,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>541.762958071971</v>
+        <v>50.511720039617</v>
       </c>
     </row>
     <row r="11">
@@ -5495,7 +5864,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>548.833667889527</v>
+        <v>151.17325396276</v>
       </c>
     </row>
     <row r="12">
@@ -5505,7 +5874,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>703.061283096893</v>
+        <v>185.055424731492</v>
       </c>
     </row>
     <row r="13">
@@ -5515,7 +5884,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>233.976428802067</v>
+        <v>59.9773974814336</v>
       </c>
     </row>
   </sheetData>
@@ -5530,16 +5899,17 @@
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="166" t="inlineStr">
         <is>
           <t>categoria</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="166" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -5552,7 +5922,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.890710382513661</v>
+        <v>0.836461126005362</v>
       </c>
     </row>
     <row r="3">
@@ -5562,7 +5932,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.577332597207982</v>
+        <v>0.799003322259136</v>
       </c>
     </row>
     <row r="4">
@@ -5572,7 +5942,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.120171673819742</v>
+        <v>0.0534351145038168</v>
       </c>
     </row>
     <row r="5">
@@ -5582,7 +5952,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.0236993409059038</v>
+        <v>0.0144092219020173</v>
       </c>
     </row>
     <row r="6">
@@ -5592,7 +5962,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.840901630375315</v>
+        <v>0.842022116903633</v>
       </c>
     </row>
     <row r="7">
@@ -5602,7 +5972,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.932130398542895</v>
+        <v>0.794378564316104</v>
       </c>
     </row>
     <row r="8">
@@ -5612,7 +5982,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.917563011719377</v>
+        <v>0.892394965431661</v>
       </c>
     </row>
     <row r="9">
@@ -5622,7 +5992,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.785294361182413</v>
+        <v>0.781211750305998</v>
       </c>
     </row>
     <row r="10">
@@ -5632,7 +6002,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.586227909811091</v>
+        <v>0.0065359477124183</v>
       </c>
     </row>
     <row r="11">
@@ -5642,7 +6012,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.263715474839198</v>
+        <v>0.263278388278388</v>
       </c>
     </row>
     <row r="12">
@@ -5652,7 +6022,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.805081284208806</v>
+        <v>0.794537554314091</v>
       </c>
     </row>
     <row r="13">
@@ -5662,7 +6032,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.0348456097981715</v>
+        <v>0.0121130551816958</v>
       </c>
     </row>
   </sheetData>
@@ -5677,29 +6047,29 @@
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="168" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="168" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="168" t="inlineStr">
         <is>
           <t>Déficit cuantitativo de vivienda</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="168" t="inlineStr">
         <is>
           <t>Déficit cualitativo de vivienda</t>
         </is>
@@ -5909,47 +6279,47 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="77.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="78.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="36" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="36" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="36" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="36" t="inlineStr">
         <is>
           <t>Km de vía primaria por km² del municipio</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="36" t="inlineStr">
         <is>
           <t>Km de vía secundaria por km² del municipio</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="36" t="inlineStr">
         <is>
           <t>Km de vía terciaria por km² del municipio</t>
         </is>
@@ -5974,13 +6344,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="38">
         <v>0</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="40">
         <v>0.147958186265097</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="42">
         <v>0.374313104964256</v>
       </c>
     </row>
@@ -6003,13 +6373,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="38">
         <v>0.135374156084845</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="40">
         <v>0.0884335556852994</v>
       </c>
-      <c r="G3" s="36">
+      <c r="G3" s="42">
         <v>0.276008411034551</v>
       </c>
     </row>
@@ -6032,13 +6402,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="38">
         <v>0</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="40">
         <v>0.157627657451121</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="42">
         <v>0.211128132497236</v>
       </c>
     </row>
@@ -6061,13 +6431,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="38">
         <v>0</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="40">
         <v>0.151209969026274</v>
       </c>
-      <c r="G5" s="36">
+      <c r="G5" s="42">
         <v>0.696673873086198</v>
       </c>
     </row>
@@ -6090,13 +6460,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="38">
         <v>0</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="40">
         <v>0.310621664969213</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="42">
         <v>0.308742094255979</v>
       </c>
     </row>
@@ -6119,13 +6489,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="38">
         <v>0.106724612864702</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="40">
         <v>0.154081510315185</v>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="42">
         <v>1.20571349214972</v>
       </c>
     </row>
@@ -6148,13 +6518,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="38">
         <v>0</v>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="40">
         <v>0.183882908654111</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="42">
         <v>1.03540236974388</v>
       </c>
     </row>
@@ -6177,13 +6547,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="38">
         <v>0</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="40">
         <v>0.102621891113972</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="42">
         <v>0.22667865701666</v>
       </c>
     </row>
@@ -6206,13 +6576,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="38">
         <v>0.0131566917206373</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="40">
         <v>0.0145852532517678</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="42">
         <v>0.236811192698039</v>
       </c>
     </row>
@@ -6235,13 +6605,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="38">
         <v>0.0910702178978712</v>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="40">
         <v>0.0437556153458644</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="42">
         <v>0.165076879897097</v>
       </c>
     </row>
@@ -6264,13 +6634,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="38">
         <v>0</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="40">
         <v>0.0973307557822368</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="42">
         <v>0.307089602841772</v>
       </c>
     </row>
@@ -6293,44 +6663,44 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="38">
         <v>0</v>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="40">
         <v>0.224833422580404</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="42">
         <v>0.831383632173415</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por área del municipio)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="33">
+      <c r="C14" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="39">
         <v>0.0278659794706636</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="41">
         <v>0.110640033158553</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="43">
         <v>0.377369022240852</v>
       </c>
     </row>
@@ -6346,47 +6716,47 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="68.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="69.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="45" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="45" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="45" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="45" t="inlineStr">
         <is>
           <t>Km de vía primaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Km de vía secundaria por cada 1.000 hab.</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="45" t="inlineStr">
         <is>
           <t>Km de vía terciaria por cada 1.000 hab.</t>
         </is>
@@ -6411,13 +6781,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="47">
         <v>0</v>
       </c>
-      <c r="F2" s="40">
+      <c r="F2" s="49">
         <v>3.88366602935879</v>
       </c>
-      <c r="G2" s="42">
+      <c r="G2" s="51">
         <v>9.82512104797554</v>
       </c>
     </row>
@@ -6440,13 +6810,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="47">
         <v>2.13054282782439</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="49">
         <v>1.39178321219774</v>
       </c>
-      <c r="G3" s="42">
+      <c r="G3" s="51">
         <v>4.34387003809142</v>
       </c>
     </row>
@@ -6469,13 +6839,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="47">
         <v>0</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="49">
         <v>6.34449706097353</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="51">
         <v>8.49788569961403</v>
       </c>
     </row>
@@ -6498,13 +6868,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="38">
+      <c r="E5" s="47">
         <v>0</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="49">
         <v>2.6882181964825</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="51">
         <v>12.3855020585239</v>
       </c>
     </row>
@@ -6527,13 +6897,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="47">
         <v>0</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="49">
         <v>2.89358714779117</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="51">
         <v>2.87607806110298</v>
       </c>
     </row>
@@ -6556,13 +6926,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="47">
         <v>0.17281751791141</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="49">
         <v>0.249501810819109</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="51">
         <v>1.95239324306351</v>
       </c>
     </row>
@@ -6585,13 +6955,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="47">
         <v>0</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="49">
         <v>0.970816009532258</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="51">
         <v>5.46644168407073</v>
       </c>
     </row>
@@ -6614,13 +6984,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="47">
         <v>0</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="49">
         <v>4.36937801658422</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="51">
         <v>9.65139825475872</v>
       </c>
     </row>
@@ -6643,13 +7013,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="47">
         <v>0.78439005729413</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="49">
         <v>0.869559603335404</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="51">
         <v>14.1184690614085</v>
       </c>
     </row>
@@ -6672,13 +7042,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="47">
         <v>3.45056653752802</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="49">
         <v>1.6578598978505</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="51">
         <v>6.25461068437577</v>
       </c>
     </row>
@@ -6701,13 +7071,13 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="47">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="49">
         <v>2.14818675287862</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="51">
         <v>6.77777349481803</v>
       </c>
     </row>
@@ -6730,44 +7100,44 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="47">
         <v>0</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="49">
         <v>2.21945777515079</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="51">
         <v>8.20705767577999</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por población)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="39">
+      <c r="C14" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="48">
         <v>0.461952204065123</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="50">
         <v>1.6638909421838</v>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="52">
         <v>5.67124905029651</v>
       </c>
     </row>
@@ -6783,71 +7153,71 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="52.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="54.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="53.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral total ($)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral urbano ($)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>Avalúo catastral rural ($)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral urbano sobre el total</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>Proporción del avalúo catastral rural sobre el total</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro rural</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>Estado del catastro urbano</t>
         </is>
@@ -6872,19 +7242,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="56">
         <v>305363283153</v>
       </c>
-      <c r="F2" s="46">
+      <c r="F2" s="58">
         <v>125537307008</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="60">
         <v>179825976145</v>
       </c>
-      <c r="H2" s="50">
+      <c r="H2" s="62">
         <v>0.411108060248031</v>
       </c>
-      <c r="I2" s="52">
+      <c r="I2" s="64">
         <v>0.588891939751969</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -6917,19 +7287,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="56">
         <v>914059114887</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="58">
         <v>313407020000</v>
       </c>
-      <c r="G3" s="48">
+      <c r="G3" s="60">
         <v>600652094887</v>
       </c>
-      <c r="H3" s="50">
+      <c r="H3" s="62">
         <v>0.342873907054408</v>
       </c>
-      <c r="I3" s="52">
+      <c r="I3" s="64">
         <v>0.657126092945592</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -6962,19 +7332,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="56">
         <v>214936655003</v>
       </c>
-      <c r="F4" s="46">
+      <c r="F4" s="58">
         <v>123234866003</v>
       </c>
-      <c r="G4" s="48">
+      <c r="G4" s="60">
         <v>91701789000</v>
       </c>
-      <c r="H4" s="50">
+      <c r="H4" s="62">
         <v>0.573354349453703</v>
       </c>
-      <c r="I4" s="52">
+      <c r="I4" s="64">
         <v>0.426645650546297</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -7007,19 +7377,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="56">
         <v>460455723000</v>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="58">
         <v>165130445000</v>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="60">
         <v>295325278000</v>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="62">
         <v>0.358623938745137</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="64">
         <v>0.641376061254862</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -7052,19 +7422,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="56">
         <v>2886390742000</v>
       </c>
-      <c r="F6" s="46">
+      <c r="F6" s="58">
         <v>1140332826000</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="60">
         <v>1746057916000</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="62">
         <v>0.395072229621224</v>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="64">
         <v>0.604927770378776</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -7097,19 +7467,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="56">
         <v>2667926824000</v>
       </c>
-      <c r="F7" s="46">
+      <c r="F7" s="58">
         <v>509419646000</v>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="60">
         <v>2158507178000</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="62">
         <v>0.190942135825237</v>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="64">
         <v>0.809057864174763</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -7142,19 +7512,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="56">
         <v>2181961922281</v>
       </c>
-      <c r="F8" s="46">
+      <c r="F8" s="58">
         <v>583846095000</v>
       </c>
-      <c r="G8" s="48">
+      <c r="G8" s="60">
         <v>1598115827281</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8" s="62">
         <v>0.267578498523775</v>
       </c>
-      <c r="I8" s="52">
+      <c r="I8" s="64">
         <v>0.732421501476225</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -7187,19 +7557,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="56">
         <v>150529182000</v>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="58">
         <v>87370277000</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="60">
         <v>63158905000</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9" s="62">
         <v>0.58042085819612</v>
       </c>
-      <c r="I9" s="52">
+      <c r="I9" s="64">
         <v>0.41957914180388</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -7232,19 +7602,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="56">
         <v>923444677000</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="58">
         <v>126667146000</v>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="60">
         <v>796777531000</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="62">
         <v>0.137168093720031</v>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="64">
         <v>0.862831906279969</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -7277,19 +7647,19 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="56">
         <v>1424754333630</v>
       </c>
-      <c r="F11" s="46">
+      <c r="F11" s="58">
         <v>526305420000</v>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="60">
         <v>898448913630</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="62">
         <v>0.369400820602577</v>
       </c>
-      <c r="I11" s="52">
+      <c r="I11" s="64">
         <v>0.630599179397423</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -7304,47 +7674,47 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E12" s="45">
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E12" s="57">
         <v>12129822456954</v>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="59">
         <v>3701251048011</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="61">
         <v>8428571408943</v>
       </c>
-      <c r="H12" s="51">
+      <c r="H12" s="63">
         <v>0.305136456955236</v>
       </c>
-      <c r="I12" s="53">
+      <c r="I12" s="65">
         <v>0.694863543044764</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" s="55" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -7362,100 +7732,100 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="23.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="15" max="16" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="67" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="67" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="67" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="67" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="67" t="inlineStr">
         <is>
           <t>IMCA total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="67" t="inlineStr">
         <is>
           <t>IMCA adopción TIC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="67" t="inlineStr">
         <is>
           <t>IMCA capacidades</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="67" t="inlineStr">
         <is>
           <t>IMCA dinamismo de los negocios</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="67" t="inlineStr">
         <is>
           <t>IMCA infraestructura</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="67" t="inlineStr">
         <is>
           <t>IMCA innovación</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="67" t="inlineStr">
         <is>
           <t>IMCA instituciones</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado de bienes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="67" t="inlineStr">
         <is>
           <t>IMCA mercado laboral</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="67" t="inlineStr">
         <is>
           <t>IMCA salud</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="67" t="inlineStr">
         <is>
           <t>IMCA sistema financiero</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="67" t="inlineStr">
         <is>
           <t>IMCA tamaño del mercado</t>
         </is>
@@ -7480,40 +7850,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="54">
+      <c r="E2" s="69">
         <v>33.2781128578734</v>
       </c>
-      <c r="F2" s="56">
+      <c r="F2" s="71">
         <v>4.99133484243419</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="73">
         <v>42.3116440585194</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="75">
         <v>68.866661801741</v>
       </c>
-      <c r="I2" s="62">
+      <c r="I2" s="77">
         <v>54.7966554040247</v>
       </c>
-      <c r="J2" s="64">
+      <c r="J2" s="79">
         <v>0</v>
       </c>
-      <c r="K2" s="66">
+      <c r="K2" s="81">
         <v>58.3867114085176</v>
       </c>
-      <c r="L2" s="68">
+      <c r="L2" s="83">
         <v>10.4021166111027</v>
       </c>
-      <c r="M2" s="70">
+      <c r="M2" s="85">
         <v>36.5478818245032</v>
       </c>
-      <c r="N2" s="72">
+      <c r="N2" s="87">
         <v>50.7701353094635</v>
       </c>
-      <c r="O2" s="74">
+      <c r="O2" s="89">
         <v>21.3081944862665</v>
       </c>
-      <c r="P2" s="76">
+      <c r="P2" s="91">
         <v>17.6779056900351</v>
       </c>
     </row>
@@ -7536,40 +7906,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="69">
         <v>32.2516355482381</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="71">
         <v>21.1170348792849</v>
       </c>
-      <c r="G3" s="58">
+      <c r="G3" s="73">
         <v>52.785485940055</v>
       </c>
-      <c r="H3" s="60">
+      <c r="H3" s="75">
         <v>63.7362654381114</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="77">
         <v>46.0578268316045</v>
       </c>
-      <c r="J3" s="64">
+      <c r="J3" s="79">
         <v>0</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="81">
         <v>47.3482659104854</v>
       </c>
-      <c r="L3" s="68">
+      <c r="L3" s="83">
         <v>7.17768002783472</v>
       </c>
-      <c r="M3" s="70">
+      <c r="M3" s="85">
         <v>28.8655563742746</v>
       </c>
-      <c r="N3" s="72">
+      <c r="N3" s="87">
         <v>47.8968721298911</v>
       </c>
-      <c r="O3" s="74">
+      <c r="O3" s="89">
         <v>19.5670357688069</v>
       </c>
-      <c r="P3" s="76">
+      <c r="P3" s="91">
         <v>20.2159677302705</v>
       </c>
     </row>
@@ -7592,40 +7962,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="69">
         <v>34.6046940544983</v>
       </c>
-      <c r="F4" s="56">
+      <c r="F4" s="71">
         <v>6.48510663348584</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="73">
         <v>41.5072014841847</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="75">
         <v>64.8790408450186</v>
       </c>
-      <c r="I4" s="62">
+      <c r="I4" s="77">
         <v>55.8250691763073</v>
       </c>
-      <c r="J4" s="64">
+      <c r="J4" s="79">
         <v>0</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="81">
         <v>50.6741478249157</v>
       </c>
-      <c r="L4" s="68">
+      <c r="L4" s="83">
         <v>7.22128316769788</v>
       </c>
-      <c r="M4" s="70">
+      <c r="M4" s="85">
         <v>59.5594145802782</v>
       </c>
-      <c r="N4" s="72">
+      <c r="N4" s="87">
         <v>51.2151350497993</v>
       </c>
-      <c r="O4" s="74">
+      <c r="O4" s="89">
         <v>20.54257968696</v>
       </c>
-      <c r="P4" s="76">
+      <c r="P4" s="91">
         <v>22.7426561508337</v>
       </c>
     </row>
@@ -7648,40 +8018,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="69">
         <v>34.4856981287114</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="71">
         <v>26.8525628429441</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="73">
         <v>40.7814305403374</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="75">
         <v>68.2831077570309</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="77">
         <v>50.7865563848946</v>
       </c>
-      <c r="J5" s="64">
+      <c r="J5" s="79">
         <v>0</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="81">
         <v>50.0584862563127</v>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="83">
         <v>11.6047390079135</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="85">
         <v>43.0804154104368</v>
       </c>
-      <c r="N5" s="72">
+      <c r="N5" s="87">
         <v>51.3390113337753</v>
       </c>
-      <c r="O5" s="74">
+      <c r="O5" s="89">
         <v>18.2609721426813</v>
       </c>
-      <c r="P5" s="76">
+      <c r="P5" s="91">
         <v>18.2953977394987</v>
       </c>
     </row>
@@ -7704,40 +8074,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="69">
         <v>41.4458132723024</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="71">
         <v>16.9380253648129</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="73">
         <v>62.9765580416544</v>
       </c>
-      <c r="H6" s="60">
+      <c r="H6" s="75">
         <v>76.1523839497832</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="77">
         <v>57.8567415768054</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="79">
         <v>0</v>
       </c>
-      <c r="K6" s="66">
+      <c r="K6" s="81">
         <v>69.3998574254504</v>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="83">
         <v>25.4830360803608</v>
       </c>
-      <c r="M6" s="70">
+      <c r="M6" s="85">
         <v>51.2831947368087</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="87">
         <v>49.1652133742958</v>
       </c>
-      <c r="O6" s="74">
+      <c r="O6" s="89">
         <v>16.7815376230313</v>
       </c>
-      <c r="P6" s="76">
+      <c r="P6" s="91">
         <v>29.8673978223238</v>
       </c>
     </row>
@@ -7760,40 +8130,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="69">
         <v>46.4601866993245</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="71">
         <v>31.8525579592976</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="73">
         <v>54.1116617868818</v>
       </c>
-      <c r="H7" s="60">
+      <c r="H7" s="75">
         <v>72.8382327508291</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="77">
         <v>62.4341444121099</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="79">
         <v>0</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="81">
         <v>56.523490489068</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="83">
         <v>30.8760592227931</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="85">
         <v>54.9935398625801</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="87">
         <v>46.6635558040389</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="89">
         <v>31.3875332069769</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="91">
         <v>69.3812781979938</v>
       </c>
     </row>
@@ -7816,40 +8186,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="69">
         <v>35.549541004035</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="71">
         <v>28.3431981975113</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="73">
         <v>51.6885154683082</v>
       </c>
-      <c r="H8" s="60">
+      <c r="H8" s="75">
         <v>69.4875612592845</v>
       </c>
-      <c r="I8" s="62">
+      <c r="I8" s="77">
         <v>57.4671691965839</v>
       </c>
-      <c r="J8" s="64">
+      <c r="J8" s="79">
         <v>0</v>
       </c>
-      <c r="K8" s="66">
+      <c r="K8" s="81">
         <v>44.3347726770515</v>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="83">
         <v>9.07382472130709</v>
       </c>
-      <c r="M8" s="70">
+      <c r="M8" s="85">
         <v>37.5954083613335</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="87">
         <v>49.623238661251</v>
       </c>
-      <c r="O8" s="74">
+      <c r="O8" s="89">
         <v>22.474849554511</v>
       </c>
-      <c r="P8" s="76">
+      <c r="P8" s="91">
         <v>20.9564129472435</v>
       </c>
     </row>
@@ -7872,40 +8242,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="69">
         <v>32.7530370325061</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="71">
         <v>6.6759789704116</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="73">
         <v>49.5966278365805</v>
       </c>
-      <c r="H9" s="60">
+      <c r="H9" s="75">
         <v>60.86892430666</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="77">
         <v>55.2550000191141</v>
       </c>
-      <c r="J9" s="64">
+      <c r="J9" s="79">
         <v>0</v>
       </c>
-      <c r="K9" s="66">
+      <c r="K9" s="81">
         <v>46.8566671531038</v>
       </c>
-      <c r="L9" s="68">
+      <c r="L9" s="83">
         <v>7.99633900477069</v>
       </c>
-      <c r="M9" s="70">
+      <c r="M9" s="85">
         <v>43.0753794805344</v>
       </c>
-      <c r="N9" s="72">
+      <c r="N9" s="87">
         <v>47.1857985695031</v>
       </c>
-      <c r="O9" s="74">
+      <c r="O9" s="89">
         <v>23.5972854985084</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="91">
         <v>19.1754065183801</v>
       </c>
     </row>
@@ -7928,40 +8298,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="69">
         <v>30.0810150800892</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F10" s="71">
         <v>2.69298426864828</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="73">
         <v>44.1636154975235</v>
       </c>
-      <c r="H10" s="60">
+      <c r="H10" s="75">
         <v>63.2489809926795</v>
       </c>
-      <c r="I10" s="62">
+      <c r="I10" s="77">
         <v>32.4541632667769</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="79">
         <v>33.3333333333333</v>
       </c>
-      <c r="K10" s="66">
+      <c r="K10" s="81">
         <v>48.1374562239317</v>
       </c>
-      <c r="L10" s="68">
+      <c r="L10" s="83">
         <v>4.93970973943813</v>
       </c>
-      <c r="M10" s="70">
+      <c r="M10" s="85">
         <v>24.6347958097028</v>
       </c>
-      <c r="N10" s="72">
+      <c r="N10" s="87">
         <v>54.4837834895654</v>
       </c>
-      <c r="O10" s="74">
+      <c r="O10" s="89">
         <v>7.69548763420125</v>
       </c>
-      <c r="P10" s="76">
+      <c r="P10" s="91">
         <v>15.1068556251807</v>
       </c>
     </row>
@@ -7984,40 +8354,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="69">
         <v>34.0234825221669</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="71">
         <v>50.9671396670554</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="73">
         <v>51.6884552712674</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="75">
         <v>61.1612047432349</v>
       </c>
-      <c r="I11" s="62">
+      <c r="I11" s="77">
         <v>45.8792731271807</v>
       </c>
-      <c r="J11" s="64">
+      <c r="J11" s="79">
         <v>0</v>
       </c>
-      <c r="K11" s="66">
+      <c r="K11" s="81">
         <v>47.1692980703228</v>
       </c>
-      <c r="L11" s="68">
+      <c r="L11" s="83">
         <v>4.80179217603454</v>
       </c>
-      <c r="M11" s="70">
+      <c r="M11" s="85">
         <v>34.4357900335948</v>
       </c>
-      <c r="N11" s="72">
+      <c r="N11" s="87">
         <v>45.1626174872364</v>
       </c>
-      <c r="O11" s="74">
+      <c r="O11" s="89">
         <v>13.1340558692515</v>
       </c>
-      <c r="P11" s="76">
+      <c r="P11" s="91">
         <v>19.8586812986578</v>
       </c>
     </row>
@@ -8040,40 +8410,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="69">
         <v>32.5398063704537</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="71">
         <v>8.12732645699968</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="73">
         <v>46.7118995263988</v>
       </c>
-      <c r="H12" s="60">
+      <c r="H12" s="75">
         <v>64.2015662541423</v>
       </c>
-      <c r="I12" s="62">
+      <c r="I12" s="77">
         <v>52.8432864033492</v>
       </c>
-      <c r="J12" s="64">
+      <c r="J12" s="79">
         <v>0</v>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="81">
         <v>46.6813222405208</v>
       </c>
-      <c r="L12" s="68">
+      <c r="L12" s="83">
         <v>23.1421306377252</v>
       </c>
-      <c r="M12" s="70">
+      <c r="M12" s="85">
         <v>33.814271057925</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="87">
         <v>44.0826297014718</v>
       </c>
-      <c r="O12" s="74">
+      <c r="O12" s="89">
         <v>24.1906905362082</v>
       </c>
-      <c r="P12" s="76">
+      <c r="P12" s="91">
         <v>14.1427472602494</v>
       </c>
     </row>
@@ -8096,156 +8466,156 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="69">
         <v>35.1290172380124</v>
       </c>
-      <c r="F13" s="56">
+      <c r="F13" s="71">
         <v>25.9793177144041</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="73">
         <v>47.1955084623692</v>
       </c>
-      <c r="H13" s="60">
+      <c r="H13" s="75">
         <v>67.6646516671463</v>
       </c>
-      <c r="I13" s="62">
+      <c r="I13" s="77">
         <v>59.8772453378065</v>
       </c>
-      <c r="J13" s="64">
+      <c r="J13" s="79">
         <v>0</v>
       </c>
-      <c r="K13" s="66">
+      <c r="K13" s="81">
         <v>49.4218738535767</v>
       </c>
-      <c r="L13" s="68">
+      <c r="L13" s="83">
         <v>4.27486860721805</v>
       </c>
-      <c r="M13" s="70">
+      <c r="M13" s="85">
         <v>46.4054616000531</v>
       </c>
-      <c r="N13" s="72">
+      <c r="N13" s="87">
         <v>45.8153313491942</v>
       </c>
-      <c r="O13" s="74">
+      <c r="O13" s="89">
         <v>16.662287413834</v>
       </c>
-      <c r="P13" s="76">
+      <c r="P13" s="91">
         <v>23.1226436125345</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="68" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por población 2022)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="55">
+      <c r="C14" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="70">
         <v>38.2050130758763</v>
       </c>
-      <c r="F14" s="57">
+      <c r="F14" s="72">
         <v>24.5411778475292</v>
       </c>
-      <c r="G14" s="59">
+      <c r="G14" s="74">
         <v>50.7831558726617</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="76">
         <v>68.2397574230343</v>
       </c>
-      <c r="I14" s="63">
+      <c r="I14" s="78">
         <v>56.0837708506693</v>
       </c>
-      <c r="J14" s="65">
+      <c r="J14" s="80">
         <v>0.927445211421674</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="82">
         <v>51.5411863514721</v>
       </c>
-      <c r="L14" s="69">
+      <c r="L14" s="84">
         <v>16.8823185032228</v>
       </c>
-      <c r="M14" s="71">
+      <c r="M14" s="86">
         <v>44.4413361143197</v>
       </c>
-      <c r="N14" s="73">
+      <c r="N14" s="88">
         <v>47.4777975911065</v>
       </c>
-      <c r="O14" s="75">
+      <c r="O14" s="90">
         <v>23.1988763864228</v>
       </c>
-      <c r="P14" s="77">
+      <c r="P14" s="92">
         <v>36.1383216827797</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="68" t="inlineStr">
         <is>
           <t>SUBREGIÓN ORIENTE (IMCA oficial de subregión)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="55">
+      <c r="C15" s="68" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D15" s="68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="70">
         <v>38.0248978890089</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="72">
         <v>18.4375370762475</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="74">
         <v>49.4903673402077</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="76">
         <v>67.6966957604072</v>
       </c>
-      <c r="I15" s="63">
+      <c r="I15" s="78">
         <v>54.3908125539099</v>
       </c>
-      <c r="J15" s="65">
+      <c r="J15" s="80">
         <v>5.64173747282754</v>
       </c>
-      <c r="K15" s="67">
+      <c r="K15" s="82">
         <v>54.0895024743037</v>
       </c>
-      <c r="L15" s="69">
+      <c r="L15" s="84">
         <v>19.5759466880041</v>
       </c>
-      <c r="M15" s="71">
+      <c r="M15" s="86">
         <v>47.4841671624964</v>
       </c>
-      <c r="N15" s="73">
+      <c r="N15" s="88">
         <v>49.6158056804067</v>
       </c>
-      <c r="O15" s="75">
+      <c r="O15" s="90">
         <v>23.5095162677136</v>
       </c>
-      <c r="P15" s="77">
+      <c r="P15" s="92">
         <v>28.3417883025739</v>
       </c>
     </row>
@@ -8261,101 +8631,101 @@
   <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="34.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
+    <col min="14" max="14" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="94" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="94" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="94" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="94" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="94" t="inlineStr">
         <is>
           <t>Índice de Gobierno Digital</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="94" t="inlineStr">
         <is>
           <t>Gobernanza</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="94" t="inlineStr">
         <is>
           <t>Innovación Pública Digital</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="94" t="inlineStr">
         <is>
           <t>Arquitectura</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="94" t="inlineStr">
         <is>
           <t>Seguridad y Privacidad de la Información</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="94" t="inlineStr">
         <is>
           <t>Servicios Ciudadanos Digitales</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="94" t="inlineStr">
         <is>
           <t>Cultura y Apropiación</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="94" t="inlineStr">
         <is>
           <t>Servicios y Procesos Inteligentes</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="94" t="inlineStr">
         <is>
           <t>Estado Abierto</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="94" t="inlineStr">
         <is>
           <t>Decisiones basadas en datos</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="94" t="inlineStr">
         <is>
           <t>Proyectos de Transformación Digital</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="94" t="inlineStr">
         <is>
           <t>Estrategias de Ciudades y Territorios Inteligentes</t>
         </is>
@@ -8380,42 +8750,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="96">
         <v>35.36</v>
       </c>
-      <c r="F2" s="80">
+      <c r="F2" s="98">
         <v>33.25</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="100">
         <v>0</v>
       </c>
-      <c r="H2" s="84">
+      <c r="H2" s="102">
         <v>0</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="104">
         <v>20</v>
       </c>
-      <c r="J2" s="88">
+      <c r="J2" s="106">
         <v>33.25</v>
       </c>
-      <c r="K2" s="90">
+      <c r="K2" s="108">
         <v>90</v>
       </c>
-      <c r="L2" s="92">
+      <c r="L2" s="110">
         <v>0</v>
       </c>
-      <c r="M2" s="94">
+      <c r="M2" s="112">
         <v>40</v>
       </c>
-      <c r="N2" s="96">
+      <c r="N2" s="114">
         <v>0</v>
       </c>
-      <c r="O2" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P2" s="100" t="inlineStr">
+      <c r="O2" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8440,42 +8810,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="96">
         <v>69.92</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="98">
         <v>61.06</v>
       </c>
-      <c r="G3" s="82">
+      <c r="G3" s="100">
         <v>33.25</v>
       </c>
-      <c r="H3" s="84">
+      <c r="H3" s="102">
         <v>20</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="104">
         <v>58.33</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="106">
         <v>50</v>
       </c>
-      <c r="K3" s="90">
+      <c r="K3" s="108">
         <v>87.14</v>
       </c>
-      <c r="L3" s="92">
+      <c r="L3" s="110">
         <v>25</v>
       </c>
-      <c r="M3" s="94">
+      <c r="M3" s="112">
         <v>86.59</v>
       </c>
-      <c r="N3" s="96">
+      <c r="N3" s="114">
         <v>0</v>
       </c>
-      <c r="O3" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P3" s="100" t="inlineStr">
+      <c r="O3" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8500,42 +8870,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="78">
+      <c r="E4" s="96">
         <v>69.32</v>
       </c>
-      <c r="F4" s="80">
+      <c r="F4" s="98">
         <v>55.56</v>
       </c>
-      <c r="G4" s="82">
+      <c r="G4" s="100">
         <v>0</v>
       </c>
-      <c r="H4" s="84">
+      <c r="H4" s="102">
         <v>0</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="104">
         <v>25</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="106">
         <v>0</v>
       </c>
-      <c r="K4" s="90">
+      <c r="K4" s="108">
         <v>0</v>
       </c>
-      <c r="L4" s="92">
+      <c r="L4" s="110">
         <v>25</v>
       </c>
-      <c r="M4" s="94">
+      <c r="M4" s="112">
         <v>88</v>
       </c>
-      <c r="N4" s="96">
+      <c r="N4" s="114">
         <v>72.41</v>
       </c>
-      <c r="O4" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P4" s="100" t="inlineStr">
+      <c r="O4" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8560,42 +8930,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="96">
         <v>57.01</v>
       </c>
-      <c r="F5" s="80">
+      <c r="F5" s="98">
         <v>45.83</v>
       </c>
-      <c r="G5" s="82">
+      <c r="G5" s="100">
         <v>0</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="102">
         <v>24.44</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="104">
         <v>36.08</v>
       </c>
-      <c r="J5" s="88">
+      <c r="J5" s="106">
         <v>79.25</v>
       </c>
-      <c r="K5" s="90">
+      <c r="K5" s="108">
         <v>84.29</v>
       </c>
-      <c r="L5" s="92">
+      <c r="L5" s="110">
         <v>11.11</v>
       </c>
-      <c r="M5" s="94">
+      <c r="M5" s="112">
         <v>74.09</v>
       </c>
-      <c r="N5" s="96">
+      <c r="N5" s="114">
         <v>40</v>
       </c>
-      <c r="O5" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P5" s="100" t="inlineStr">
+      <c r="O5" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8620,40 +8990,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="96">
         <v>61.06</v>
       </c>
-      <c r="F6" s="80">
+      <c r="F6" s="98">
         <v>66.75</v>
       </c>
-      <c r="G6" s="82">
+      <c r="G6" s="100">
         <v>69.33</v>
       </c>
-      <c r="H6" s="84">
+      <c r="H6" s="102">
         <v>33.33</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="104">
         <v>30</v>
       </c>
-      <c r="J6" s="88">
+      <c r="J6" s="106">
         <v>0</v>
       </c>
-      <c r="K6" s="90">
+      <c r="K6" s="108">
         <v>52</v>
       </c>
-      <c r="L6" s="92">
+      <c r="L6" s="110">
         <v>0</v>
       </c>
-      <c r="M6" s="94">
+      <c r="M6" s="112">
         <v>89.33</v>
       </c>
-      <c r="N6" s="96">
+      <c r="N6" s="114">
         <v>24.14</v>
       </c>
-      <c r="O6" s="98">
+      <c r="O6" s="116">
         <v>33.33</v>
       </c>
-      <c r="P6" s="100" t="inlineStr">
+      <c r="P6" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8678,40 +9048,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="96">
         <v>86.3</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="98">
         <v>100</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="100">
         <v>100</v>
       </c>
-      <c r="H7" s="84">
+      <c r="H7" s="102">
         <v>72.04</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="104">
         <v>82.08</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="106">
         <v>0</v>
       </c>
-      <c r="K7" s="90">
+      <c r="K7" s="108">
         <v>100</v>
       </c>
-      <c r="L7" s="92">
+      <c r="L7" s="110">
         <v>63.89</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="112">
         <v>96.34</v>
       </c>
-      <c r="N7" s="96">
+      <c r="N7" s="114">
         <v>89.66</v>
       </c>
-      <c r="O7" s="98">
+      <c r="O7" s="116">
         <v>89</v>
       </c>
-      <c r="P7" s="100">
+      <c r="P7" s="118">
         <v>66.67</v>
       </c>
     </row>
@@ -8734,40 +9104,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="96">
         <v>64.19</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="98">
         <v>66.67</v>
       </c>
-      <c r="G8" s="82">
+      <c r="G8" s="100">
         <v>83.5</v>
       </c>
-      <c r="H8" s="84">
+      <c r="H8" s="102">
         <v>58.06</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="104">
         <v>33.25</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="106">
         <v>0</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="108">
         <v>72</v>
       </c>
-      <c r="L8" s="92">
+      <c r="L8" s="110">
         <v>33.33</v>
       </c>
-      <c r="M8" s="94">
+      <c r="M8" s="112">
         <v>80</v>
       </c>
-      <c r="N8" s="96">
+      <c r="N8" s="114">
         <v>44.83</v>
       </c>
-      <c r="O8" s="98">
+      <c r="O8" s="116">
         <v>100</v>
       </c>
-      <c r="P8" s="100">
+      <c r="P8" s="118">
         <v>25</v>
       </c>
     </row>
@@ -8790,40 +9160,40 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="78">
+      <c r="E9" s="96">
         <v>51.32</v>
       </c>
-      <c r="F9" s="80">
+      <c r="F9" s="98">
         <v>79.17</v>
       </c>
-      <c r="G9" s="82">
+      <c r="G9" s="100">
         <v>0</v>
       </c>
-      <c r="H9" s="84">
+      <c r="H9" s="102">
         <v>15.87</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="104">
         <v>88.17</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="106">
         <v>25</v>
       </c>
-      <c r="K9" s="90">
+      <c r="K9" s="108">
         <v>48</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="110">
         <v>66.67</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="112">
         <v>68</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="114">
         <v>16</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="116">
         <v>11</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="118">
         <v>0</v>
       </c>
     </row>
@@ -8846,42 +9216,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="96">
         <v>52.53</v>
       </c>
-      <c r="F10" s="80">
+      <c r="F10" s="98">
         <v>61.06</v>
       </c>
-      <c r="G10" s="82">
+      <c r="G10" s="100">
         <v>0</v>
       </c>
-      <c r="H10" s="84">
+      <c r="H10" s="102">
         <v>26.67</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="104">
         <v>38.64</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="106">
         <v>56.25</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="108">
         <v>64</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="110">
         <v>50</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="112">
         <v>71.95</v>
       </c>
-      <c r="N10" s="96">
+      <c r="N10" s="114">
         <v>8</v>
       </c>
-      <c r="O10" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P10" s="100" t="inlineStr">
+      <c r="O10" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8906,42 +9276,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="96">
         <v>67.55</v>
       </c>
-      <c r="F11" s="80">
+      <c r="F11" s="98">
         <v>58.33</v>
       </c>
-      <c r="G11" s="82">
+      <c r="G11" s="100">
         <v>0</v>
       </c>
-      <c r="H11" s="84">
+      <c r="H11" s="102">
         <v>33.33</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="104">
         <v>47.73</v>
       </c>
-      <c r="J11" s="88">
+      <c r="J11" s="106">
         <v>0</v>
       </c>
-      <c r="K11" s="90">
+      <c r="K11" s="108">
         <v>68</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="110">
         <v>25</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="112">
         <v>81.33</v>
       </c>
-      <c r="N11" s="96">
+      <c r="N11" s="114">
         <v>0</v>
       </c>
-      <c r="O11" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P11" s="100" t="inlineStr">
+      <c r="O11" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -8966,42 +9336,42 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="96">
         <v>45.89</v>
       </c>
-      <c r="F12" s="80">
+      <c r="F12" s="98">
         <v>50.08</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="100">
         <v>0</v>
       </c>
-      <c r="H12" s="84">
+      <c r="H12" s="102">
         <v>37.78</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="104">
         <v>25</v>
       </c>
-      <c r="J12" s="88">
+      <c r="J12" s="106">
         <v>66.67</v>
       </c>
-      <c r="K12" s="90">
+      <c r="K12" s="108">
         <v>44</v>
       </c>
-      <c r="L12" s="92">
+      <c r="L12" s="110">
         <v>0</v>
       </c>
-      <c r="M12" s="94">
+      <c r="M12" s="112">
         <v>62.67</v>
       </c>
-      <c r="N12" s="96">
+      <c r="N12" s="114">
         <v>12</v>
       </c>
-      <c r="O12" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P12" s="100" t="inlineStr">
+      <c r="O12" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -9026,160 +9396,160 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="96">
         <v>36.6</v>
       </c>
-      <c r="F13" s="80">
+      <c r="F13" s="98">
         <v>58.33</v>
       </c>
-      <c r="G13" s="82">
+      <c r="G13" s="100">
         <v>0</v>
       </c>
-      <c r="H13" s="84">
+      <c r="H13" s="102">
         <v>16.67</v>
       </c>
-      <c r="I13" s="86">
+      <c r="I13" s="104">
         <v>0</v>
       </c>
-      <c r="J13" s="88">
+      <c r="J13" s="106">
         <v>0</v>
       </c>
-      <c r="K13" s="90">
+      <c r="K13" s="108">
         <v>0</v>
       </c>
-      <c r="L13" s="92">
+      <c r="L13" s="110">
         <v>25</v>
       </c>
-      <c r="M13" s="94">
+      <c r="M13" s="112">
         <v>44</v>
       </c>
-      <c r="N13" s="96">
+      <c r="N13" s="114">
         <v>0</v>
       </c>
-      <c r="O13" s="98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P13" s="100" t="inlineStr">
+      <c r="O13" s="116" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" s="118" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGUA, BOSQUES Y TURISMO (por población 2024)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="79">
+      <c r="C14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="97">
         <v>65.2177727264301</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="99">
         <v>73.07787440218</v>
       </c>
-      <c r="G14" s="83">
+      <c r="G14" s="101">
         <v>46.5832005616728</v>
       </c>
-      <c r="H14" s="85">
+      <c r="H14" s="103">
         <v>42.411814360657</v>
       </c>
-      <c r="I14" s="87">
+      <c r="I14" s="105">
         <v>51.6336411411411</v>
       </c>
-      <c r="J14" s="89">
+      <c r="J14" s="107">
         <v>17.2243789622956</v>
       </c>
-      <c r="K14" s="91">
+      <c r="K14" s="109">
         <v>68.3583944592741</v>
       </c>
-      <c r="L14" s="93">
+      <c r="L14" s="111">
         <v>38.205539845401</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="113">
         <v>78.8157197938679</v>
       </c>
-      <c r="N14" s="97">
+      <c r="N14" s="115">
         <v>40.8450623308494</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="117">
         <v>75.6796344118689</v>
       </c>
-      <c r="P14" s="101">
+      <c r="P14" s="119">
         <v>47.7273111423717</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B15" s="95" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN ORIENTE (por población 2024)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>ORIENTE</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E15" s="79">
+      <c r="C15" s="95" t="inlineStr">
+        <is>
+          <t>ORIENTE</t>
+        </is>
+      </c>
+      <c r="D15" s="95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="97">
         <v>69.9987273225564</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="99">
         <v>74.2393150709581</v>
       </c>
-      <c r="G15" s="83">
+      <c r="G15" s="101">
         <v>71.8718556505539</v>
       </c>
-      <c r="H15" s="85">
+      <c r="H15" s="103">
         <v>51.3964209952261</v>
       </c>
-      <c r="I15" s="87">
+      <c r="I15" s="105">
         <v>64.2195546798548</v>
       </c>
-      <c r="J15" s="89">
+      <c r="J15" s="107">
         <v>8.07280470165502</v>
       </c>
-      <c r="K15" s="91">
+      <c r="K15" s="109">
         <v>78.6565040160893</v>
       </c>
-      <c r="L15" s="93">
+      <c r="L15" s="111">
         <v>29.8154914466918</v>
       </c>
-      <c r="M15" s="95">
+      <c r="M15" s="113">
         <v>82.6214629139797</v>
       </c>
-      <c r="N15" s="97">
+      <c r="N15" s="115">
         <v>57.3958395031482</v>
       </c>
-      <c r="O15" s="99">
+      <c r="O15" s="117">
         <v>71.7110861617901</v>
       </c>
-      <c r="P15" s="101">
+      <c r="P15" s="119">
         <v>74.0707792182963</v>
       </c>
     </row>
@@ -9195,35 +9565,35 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="51.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="121" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="121" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="121" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="121" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="121" t="inlineStr">
         <is>
           <t>Tasa de tránsito inmediato a la educación superior</t>
         </is>
@@ -9248,7 +9618,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="123">
         <v>0.272727272727273</v>
       </c>
     </row>
@@ -9271,7 +9641,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="123">
         <v>0.280701754385965</v>
       </c>
     </row>
@@ -9294,7 +9664,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="123">
         <v>0.239130434782609</v>
       </c>
     </row>
@@ -9317,7 +9687,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="123">
         <v>0.287128712871287</v>
       </c>
     </row>
@@ -9340,7 +9710,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="102">
+      <c r="E6" s="123">
         <v>0.274509803921569</v>
       </c>
     </row>
@@ -9363,7 +9733,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="102">
+      <c r="E7" s="123">
         <v>0.365329512893983</v>
       </c>
     </row>
@@ -9386,7 +9756,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="102">
+      <c r="E8" s="123">
         <v>0.437158469945355</v>
       </c>
     </row>
@@ -9409,7 +9779,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="102">
+      <c r="E9" s="123">
         <v>0.284153005464481</v>
       </c>
     </row>
@@ -9432,7 +9802,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="102">
+      <c r="E10" s="123">
         <v>0.181818181818182</v>
       </c>
     </row>
@@ -9455,7 +9825,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="102">
+      <c r="E11" s="123">
         <v>0.374149659863946</v>
       </c>
     </row>
@@ -9478,7 +9848,7 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="102">
+      <c r="E12" s="123">
         <v>0.3828125</v>
       </c>
     </row>
@@ -9501,32 +9871,32 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="102">
+      <c r="E13" s="123">
         <v>0.350785340314136</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="122" t="inlineStr">
         <is>
           <t>PROMEDIO SIMPLE PROVINCIA AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="103">
+      <c r="C14" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="122" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="124">
         <v>0.310867054082399</v>
       </c>
     </row>
@@ -9542,53 +9912,53 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="37.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="32.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="58.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="89.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="33.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="59.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="126" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="126" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="126" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="126" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por fibra óptica</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="126" t="inlineStr">
         <is>
           <t>Proporción de líneas sobre fibra óptica</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="126" t="inlineStr">
         <is>
           <t>Líneas de acceso a internet fijo por cada 1.000 habitantes</t>
         </is>
@@ -9613,17 +9983,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E2" s="104">
-        <v>1464</v>
-      </c>
-      <c r="F2" s="106">
-        <v>1304</v>
-      </c>
-      <c r="G2" s="108">
-        <v>0.890710382513661</v>
-      </c>
-      <c r="H2" s="110">
-        <v>277.010406811731</v>
+      <c r="E2" s="128">
+        <v>373</v>
+      </c>
+      <c r="F2" s="130">
+        <v>312</v>
+      </c>
+      <c r="G2" s="132">
+        <v>0.836461126005362</v>
+      </c>
+      <c r="H2" s="134">
+        <v>70.5771050141911</v>
       </c>
     </row>
     <row r="3">
@@ -9645,17 +10015,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E3" s="104">
-        <v>12679</v>
-      </c>
-      <c r="F3" s="106">
-        <v>7320</v>
-      </c>
-      <c r="G3" s="108">
-        <v>0.577332597207982</v>
-      </c>
-      <c r="H3" s="110">
-        <v>788.053949903661</v>
+      <c r="E3" s="128">
+        <v>2408</v>
+      </c>
+      <c r="F3" s="130">
+        <v>1924</v>
+      </c>
+      <c r="G3" s="132">
+        <v>0.799003322259136</v>
+      </c>
+      <c r="H3" s="134">
+        <v>149.667474672136</v>
       </c>
     </row>
     <row r="4">
@@ -9677,17 +10047,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E4" s="104">
-        <v>466</v>
-      </c>
-      <c r="F4" s="106">
-        <v>56</v>
-      </c>
-      <c r="G4" s="108">
-        <v>0.120171673819742</v>
-      </c>
-      <c r="H4" s="110">
-        <v>91.1580594679186</v>
+      <c r="E4" s="128">
+        <v>131</v>
+      </c>
+      <c r="F4" s="130">
+        <v>7</v>
+      </c>
+      <c r="G4" s="132">
+        <v>0.0534351145038168</v>
+      </c>
+      <c r="H4" s="134">
+        <v>25.6259780907668</v>
       </c>
     </row>
     <row r="5">
@@ -9709,17 +10079,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E5" s="104">
-        <v>7131</v>
-      </c>
-      <c r="F5" s="106">
-        <v>169</v>
-      </c>
-      <c r="G5" s="108">
-        <v>0.0236993409059038</v>
-      </c>
-      <c r="H5" s="110">
-        <v>678.432118732756</v>
+      <c r="E5" s="128">
+        <v>1735</v>
+      </c>
+      <c r="F5" s="130">
+        <v>25</v>
+      </c>
+      <c r="G5" s="132">
+        <v>0.0144092219020173</v>
+      </c>
+      <c r="H5" s="134">
+        <v>165.065169822091</v>
       </c>
     </row>
     <row r="6">
@@ -9741,17 +10111,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E6" s="104">
-        <v>9139</v>
-      </c>
-      <c r="F6" s="106">
-        <v>7685</v>
-      </c>
-      <c r="G6" s="108">
-        <v>0.840901630375315</v>
-      </c>
-      <c r="H6" s="110">
-        <v>942.6508509541</v>
+      <c r="E6" s="128">
+        <v>2532</v>
+      </c>
+      <c r="F6" s="130">
+        <v>2132</v>
+      </c>
+      <c r="G6" s="132">
+        <v>0.842022116903633</v>
+      </c>
+      <c r="H6" s="134">
+        <v>261.165549252192</v>
       </c>
     </row>
     <row r="7">
@@ -9773,17 +10143,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E7" s="104">
-        <v>64786</v>
-      </c>
-      <c r="F7" s="106">
-        <v>60389</v>
-      </c>
-      <c r="G7" s="108">
-        <v>0.932130398542895</v>
-      </c>
-      <c r="H7" s="110">
-        <v>870.896625890577</v>
+      <c r="E7" s="128">
+        <v>22094</v>
+      </c>
+      <c r="F7" s="130">
+        <v>17551</v>
+      </c>
+      <c r="G7" s="132">
+        <v>0.794378564316104</v>
+      </c>
+      <c r="H7" s="134">
+        <v>297.002285253394</v>
       </c>
     </row>
     <row r="8">
@@ -9805,17 +10175,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E8" s="104">
-        <v>24916</v>
-      </c>
-      <c r="F8" s="106">
-        <v>22862</v>
-      </c>
-      <c r="G8" s="108">
-        <v>0.917563011719377</v>
-      </c>
-      <c r="H8" s="110">
-        <v>1045.70445293155</v>
+      <c r="E8" s="128">
+        <v>5641</v>
+      </c>
+      <c r="F8" s="130">
+        <v>5034</v>
+      </c>
+      <c r="G8" s="132">
+        <v>0.892394965431661</v>
+      </c>
+      <c r="H8" s="134">
+        <v>236.748226801528</v>
       </c>
     </row>
     <row r="9">
@@ -9837,17 +10207,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E9" s="104">
-        <v>12077</v>
-      </c>
-      <c r="F9" s="106">
-        <v>9484</v>
-      </c>
-      <c r="G9" s="108">
-        <v>0.785294361182413</v>
-      </c>
-      <c r="H9" s="110">
-        <v>713.012162002598</v>
+      <c r="E9" s="128">
+        <v>3268</v>
+      </c>
+      <c r="F9" s="130">
+        <v>2553</v>
+      </c>
+      <c r="G9" s="132">
+        <v>0.781211750305998</v>
+      </c>
+      <c r="H9" s="134">
+        <v>192.938953831621</v>
       </c>
     </row>
     <row r="10">
@@ -9869,17 +10239,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E10" s="104">
-        <v>3282</v>
-      </c>
-      <c r="F10" s="106">
-        <v>1924</v>
-      </c>
-      <c r="G10" s="108">
-        <v>0.586227909811091</v>
-      </c>
-      <c r="H10" s="110">
-        <v>541.762958071971</v>
+      <c r="E10" s="128">
+        <v>306</v>
+      </c>
+      <c r="F10" s="130">
+        <v>2</v>
+      </c>
+      <c r="G10" s="132">
+        <v>0.0065359477124183</v>
+      </c>
+      <c r="H10" s="134">
+        <v>50.511720039617</v>
       </c>
     </row>
     <row r="11">
@@ -9901,17 +10271,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E11" s="104">
-        <v>7929</v>
-      </c>
-      <c r="F11" s="106">
-        <v>2091</v>
-      </c>
-      <c r="G11" s="108">
-        <v>0.263715474839198</v>
-      </c>
-      <c r="H11" s="110">
-        <v>548.833667889527</v>
+      <c r="E11" s="128">
+        <v>2184</v>
+      </c>
+      <c r="F11" s="130">
+        <v>575</v>
+      </c>
+      <c r="G11" s="132">
+        <v>0.263278388278388</v>
+      </c>
+      <c r="H11" s="134">
+        <v>151.17325396276</v>
       </c>
     </row>
     <row r="12">
@@ -9933,17 +10303,17 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E12" s="104">
-        <v>12241</v>
-      </c>
-      <c r="F12" s="106">
-        <v>9855</v>
-      </c>
-      <c r="G12" s="108">
-        <v>0.805081284208806</v>
-      </c>
-      <c r="H12" s="110">
-        <v>703.061283096893</v>
+      <c r="E12" s="128">
+        <v>3222</v>
+      </c>
+      <c r="F12" s="130">
+        <v>2560</v>
+      </c>
+      <c r="G12" s="132">
+        <v>0.794537554314091</v>
+      </c>
+      <c r="H12" s="134">
+        <v>185.055424731492</v>
       </c>
     </row>
     <row r="13">
@@ -9965,51 +10335,51 @@
           <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
         </is>
       </c>
-      <c r="E13" s="104">
-        <v>5797</v>
-      </c>
-      <c r="F13" s="106">
-        <v>202</v>
-      </c>
-      <c r="G13" s="108">
-        <v>0.0348456097981715</v>
-      </c>
-      <c r="H13" s="110">
-        <v>233.976428802067</v>
+      <c r="E13" s="128">
+        <v>1486</v>
+      </c>
+      <c r="F13" s="130">
+        <v>18</v>
+      </c>
+      <c r="G13" s="132">
+        <v>0.0121130551816958</v>
+      </c>
+      <c r="H13" s="134">
+        <v>59.9773974814336</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>PROMEDIO SIMPLE PROVINCIA AGUA, BOSQUES Y TURISMO</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E14" s="105">
-        <v>13492.25</v>
-      </c>
-      <c r="F14" s="107">
-        <v>10278.4166666667</v>
-      </c>
-      <c r="G14" s="109">
-        <v>0.564806139577046</v>
-      </c>
-      <c r="H14" s="111">
-        <v>619.546080379612</v>
+      <c r="A14" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B14" s="127" t="inlineStr">
+        <is>
+          <t>PROVINCIA AGUA, BOSQUES Y TURISMO (suma de líneas; razones recalculadas sobre las sumas)</t>
+        </is>
+      </c>
+      <c r="C14" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="127" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="129">
+        <v>45380</v>
+      </c>
+      <c r="F14" s="131">
+        <v>32693</v>
+      </c>
+      <c r="G14" s="133">
+        <v>0.720427501101807</v>
+      </c>
+      <c r="H14" s="135">
+        <v>202.102975429658</v>
       </c>
     </row>
   </sheetData>
